--- a/dados/pib_rj.xlsx
+++ b/dados/pib_rj.xlsx
@@ -1,26 +1,360 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antonio.azevedo.SAD_PMN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacqu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F783FA96-9C3A-43D5-894F-BC319AEE1AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C54D99B-5F57-476A-946D-C052E8CAAF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1900D8F-63C2-42CD-97DE-5E64D15CFDA8}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="pib_rj" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabela" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="110">
+  <si>
+    <t>Município</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Angra dos Reis (RJ)</t>
+  </si>
+  <si>
+    <t>Aperibé (RJ)</t>
+  </si>
+  <si>
+    <t>Araruama (RJ)</t>
+  </si>
+  <si>
+    <t>Areal (RJ)</t>
+  </si>
+  <si>
+    <t>Armação dos Búzios (RJ)</t>
+  </si>
+  <si>
+    <t>Arraial do Cabo (RJ)</t>
+  </si>
+  <si>
+    <t>Barra do Piraí (RJ)</t>
+  </si>
+  <si>
+    <t>Barra Mansa (RJ)</t>
+  </si>
+  <si>
+    <t>Belford Roxo (RJ)</t>
+  </si>
+  <si>
+    <t>Bom Jardim (RJ)</t>
+  </si>
+  <si>
+    <t>Bom Jesus do Itabapoana (RJ)</t>
+  </si>
+  <si>
+    <t>Cabo Frio (RJ)</t>
+  </si>
+  <si>
+    <t>Cachoeiras de Macacu (RJ)</t>
+  </si>
+  <si>
+    <t>Cambuci (RJ)</t>
+  </si>
+  <si>
+    <t>Carapebus (RJ)</t>
+  </si>
+  <si>
+    <t>Comendador Levy Gasparian (RJ)</t>
+  </si>
+  <si>
+    <t>Campos dos Goytacazes (RJ)</t>
+  </si>
+  <si>
+    <t>Cantagalo (RJ)</t>
+  </si>
+  <si>
+    <t>Cardoso Moreira (RJ)</t>
+  </si>
+  <si>
+    <t>Carmo (RJ)</t>
+  </si>
+  <si>
+    <t>Casimiro de Abreu (RJ)</t>
+  </si>
+  <si>
+    <t>Conceição de Macabu (RJ)</t>
+  </si>
+  <si>
+    <t>Cordeiro (RJ)</t>
+  </si>
+  <si>
+    <t>Duas Barras (RJ)</t>
+  </si>
+  <si>
+    <t>Duque de Caxias (RJ)</t>
+  </si>
+  <si>
+    <t>Engenheiro Paulo de Frontin (RJ)</t>
+  </si>
+  <si>
+    <t>Guapimirim (RJ)</t>
+  </si>
+  <si>
+    <t>Iguaba Grande (RJ)</t>
+  </si>
+  <si>
+    <t>Itaboraí (RJ)</t>
+  </si>
+  <si>
+    <t>Itaguaí (RJ)</t>
+  </si>
+  <si>
+    <t>Italva (RJ)</t>
+  </si>
+  <si>
+    <t>Itaocara (RJ)</t>
+  </si>
+  <si>
+    <t>Itaperuna (RJ)</t>
+  </si>
+  <si>
+    <t>Itatiaia (RJ)</t>
+  </si>
+  <si>
+    <t>Japeri (RJ)</t>
+  </si>
+  <si>
+    <t>Laje do Muriaé (RJ)</t>
+  </si>
+  <si>
+    <t>Macaé (RJ)</t>
+  </si>
+  <si>
+    <t>Macuco (RJ)</t>
+  </si>
+  <si>
+    <t>Magé (RJ)</t>
+  </si>
+  <si>
+    <t>Mangaratiba (RJ)</t>
+  </si>
+  <si>
+    <t>Maricá (RJ)</t>
+  </si>
+  <si>
+    <t>Mendes (RJ)</t>
+  </si>
+  <si>
+    <t>Mesquita (RJ)</t>
+  </si>
+  <si>
+    <t>Miguel Pereira (RJ)</t>
+  </si>
+  <si>
+    <t>Miracema (RJ)</t>
+  </si>
+  <si>
+    <t>Natividade (RJ)</t>
+  </si>
+  <si>
+    <t>Nilópolis (RJ)</t>
+  </si>
+  <si>
+    <t>Niterói (RJ)</t>
+  </si>
+  <si>
+    <t>Nova Friburgo (RJ)</t>
+  </si>
+  <si>
+    <t>Nova Iguaçu (RJ)</t>
+  </si>
+  <si>
+    <t>Paracambi (RJ)</t>
+  </si>
+  <si>
+    <t>Paraíba do Sul (RJ)</t>
+  </si>
+  <si>
+    <t>Paraty (RJ)</t>
+  </si>
+  <si>
+    <t>Paty do Alferes (RJ)</t>
+  </si>
+  <si>
+    <t>Petrópolis (RJ)</t>
+  </si>
+  <si>
+    <t>Pinheiral (RJ)</t>
+  </si>
+  <si>
+    <t>Piraí (RJ)</t>
+  </si>
+  <si>
+    <t>Porciúncula (RJ)</t>
+  </si>
+  <si>
+    <t>Porto Real (RJ)</t>
+  </si>
+  <si>
+    <t>Quatis (RJ)</t>
+  </si>
+  <si>
+    <t>Queimados (RJ)</t>
+  </si>
+  <si>
+    <t>Quissamã (RJ)</t>
+  </si>
+  <si>
+    <t>Resende (RJ)</t>
+  </si>
+  <si>
+    <t>Rio Bonito (RJ)</t>
+  </si>
+  <si>
+    <t>Rio Claro (RJ)</t>
+  </si>
+  <si>
+    <t>Rio das Flores (RJ)</t>
+  </si>
+  <si>
+    <t>Rio das Ostras (RJ)</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro (RJ)</t>
+  </si>
+  <si>
+    <t>Santa Maria Madalena (RJ)</t>
+  </si>
+  <si>
+    <t>Santo Antônio de Pádua (RJ)</t>
+  </si>
+  <si>
+    <t>São Francisco de Itabapoana (RJ)</t>
+  </si>
+  <si>
+    <t>São Fidélis (RJ)</t>
+  </si>
+  <si>
+    <t>São Gonçalo (RJ)</t>
+  </si>
+  <si>
+    <t>São João da Barra (RJ)</t>
+  </si>
+  <si>
+    <t>São João de Meriti (RJ)</t>
+  </si>
+  <si>
+    <t>São José de Ubá (RJ)</t>
+  </si>
+  <si>
+    <t>São José do Vale do Rio Preto (RJ)</t>
+  </si>
+  <si>
+    <t>São Pedro da Aldeia (RJ)</t>
+  </si>
+  <si>
+    <t>São Sebastião do Alto (RJ)</t>
+  </si>
+  <si>
+    <t>Sapucaia (RJ)</t>
+  </si>
+  <si>
+    <t>Saquarema (RJ)</t>
+  </si>
+  <si>
+    <t>Seropédica (RJ)</t>
+  </si>
+  <si>
+    <t>Silva Jardim (RJ)</t>
+  </si>
+  <si>
+    <t>Sumidouro (RJ)</t>
+  </si>
+  <si>
+    <t>Tanguá (RJ)</t>
+  </si>
+  <si>
+    <t>Teresópolis (RJ)</t>
+  </si>
+  <si>
+    <t>Trajano de Moraes (RJ)</t>
+  </si>
+  <si>
+    <t>Três Rios (RJ)</t>
+  </si>
+  <si>
+    <t>Valença (RJ)</t>
+  </si>
+  <si>
+    <t>Varre-Sai (RJ)</t>
+  </si>
+  <si>
+    <t>Vassouras (RJ)</t>
+  </si>
+  <si>
+    <t>Volta Redonda (RJ)</t>
+  </si>
   <si>
     <t>Nível</t>
   </si>
@@ -28,610 +362,31 @@
     <t>Cód.</t>
   </si>
   <si>
-    <t>Município</t>
-  </si>
-  <si>
     <t>MU</t>
-  </si>
-  <si>
-    <t>Angra dos Reis (RJ)</t>
-  </si>
-  <si>
-    <t>Aperibé (RJ)</t>
-  </si>
-  <si>
-    <t>Araruama (RJ)</t>
-  </si>
-  <si>
-    <t>Areal (RJ)</t>
-  </si>
-  <si>
-    <t>Armação dos Búzios (RJ)</t>
-  </si>
-  <si>
-    <t>Arraial do Cabo (RJ)</t>
-  </si>
-  <si>
-    <t>Barra do Piraí (RJ)</t>
-  </si>
-  <si>
-    <t>Barra Mansa (RJ)</t>
-  </si>
-  <si>
-    <t>Belford Roxo (RJ)</t>
-  </si>
-  <si>
-    <t>Bom Jardim (RJ)</t>
-  </si>
-  <si>
-    <t>Bom Jesus do Itabapoana (RJ)</t>
-  </si>
-  <si>
-    <t>Cabo Frio (RJ)</t>
-  </si>
-  <si>
-    <t>Cachoeiras de Macacu (RJ)</t>
-  </si>
-  <si>
-    <t>Cambuci (RJ)</t>
-  </si>
-  <si>
-    <t>Carapebus (RJ)</t>
-  </si>
-  <si>
-    <t>Comendador Levy Gasparian (RJ)</t>
-  </si>
-  <si>
-    <t>Campos dos Goytacazes (RJ)</t>
-  </si>
-  <si>
-    <t>Cantagalo (RJ)</t>
-  </si>
-  <si>
-    <t>Cardoso Moreira (RJ)</t>
-  </si>
-  <si>
-    <t>Carmo (RJ)</t>
-  </si>
-  <si>
-    <t>Casimiro de Abreu (RJ)</t>
-  </si>
-  <si>
-    <t>Conceição de Macabu (RJ)</t>
-  </si>
-  <si>
-    <t>Cordeiro (RJ)</t>
-  </si>
-  <si>
-    <t>Duas Barras (RJ)</t>
-  </si>
-  <si>
-    <t>Duque de Caxias (RJ)</t>
-  </si>
-  <si>
-    <t>Engenheiro Paulo de Frontin (RJ)</t>
-  </si>
-  <si>
-    <t>Guapimirim (RJ)</t>
-  </si>
-  <si>
-    <t>Iguaba Grande (RJ)</t>
-  </si>
-  <si>
-    <t>Itaboraí (RJ)</t>
-  </si>
-  <si>
-    <t>Itaguaí (RJ)</t>
-  </si>
-  <si>
-    <t>Italva (RJ)</t>
-  </si>
-  <si>
-    <t>Itaocara (RJ)</t>
-  </si>
-  <si>
-    <t>Itaperuna (RJ)</t>
-  </si>
-  <si>
-    <t>Itatiaia (RJ)</t>
-  </si>
-  <si>
-    <t>Japeri (RJ)</t>
-  </si>
-  <si>
-    <t>Laje do Muriaé (RJ)</t>
-  </si>
-  <si>
-    <t>Macaé (RJ)</t>
-  </si>
-  <si>
-    <t>Macuco (RJ)</t>
-  </si>
-  <si>
-    <t>Magé (RJ)</t>
-  </si>
-  <si>
-    <t>Mangaratiba (RJ)</t>
-  </si>
-  <si>
-    <t>Maricá (RJ)</t>
-  </si>
-  <si>
-    <t>Mendes (RJ)</t>
-  </si>
-  <si>
-    <t>Mesquita (RJ)</t>
-  </si>
-  <si>
-    <t>Miguel Pereira (RJ)</t>
-  </si>
-  <si>
-    <t>Miracema (RJ)</t>
-  </si>
-  <si>
-    <t>Natividade (RJ)</t>
-  </si>
-  <si>
-    <t>Nilópolis (RJ)</t>
-  </si>
-  <si>
-    <t>Niterói (RJ)</t>
-  </si>
-  <si>
-    <t>Nova Friburgo (RJ)</t>
-  </si>
-  <si>
-    <t>Nova Iguaçu (RJ)</t>
-  </si>
-  <si>
-    <t>Paracambi (RJ)</t>
-  </si>
-  <si>
-    <t>Paraíba do Sul (RJ)</t>
-  </si>
-  <si>
-    <t>Paraty (RJ)</t>
-  </si>
-  <si>
-    <t>Paty do Alferes (RJ)</t>
-  </si>
-  <si>
-    <t>Petrópolis (RJ)</t>
-  </si>
-  <si>
-    <t>Pinheiral (RJ)</t>
-  </si>
-  <si>
-    <t>Piraí (RJ)</t>
-  </si>
-  <si>
-    <t>Porciúncula (RJ)</t>
-  </si>
-  <si>
-    <t>Porto Real (RJ)</t>
-  </si>
-  <si>
-    <t>Quatis (RJ)</t>
-  </si>
-  <si>
-    <t>Queimados (RJ)</t>
-  </si>
-  <si>
-    <t>Quissamã (RJ)</t>
-  </si>
-  <si>
-    <t>Resende (RJ)</t>
-  </si>
-  <si>
-    <t>Rio Bonito (RJ)</t>
-  </si>
-  <si>
-    <t>Rio Claro (RJ)</t>
-  </si>
-  <si>
-    <t>Rio das Flores (RJ)</t>
-  </si>
-  <si>
-    <t>Rio das Ostras (RJ)</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro (RJ)</t>
-  </si>
-  <si>
-    <t>Santa Maria Madalena (RJ)</t>
-  </si>
-  <si>
-    <t>Santo Antônio de Pádua (RJ)</t>
-  </si>
-  <si>
-    <t>São Francisco de Itabapoana (RJ)</t>
-  </si>
-  <si>
-    <t>São Fidélis (RJ)</t>
-  </si>
-  <si>
-    <t>São Gonçalo (RJ)</t>
-  </si>
-  <si>
-    <t>São João da Barra (RJ)</t>
-  </si>
-  <si>
-    <t>São João de Meriti (RJ)</t>
-  </si>
-  <si>
-    <t>São José de Ubá (RJ)</t>
-  </si>
-  <si>
-    <t>São José do Vale do Rio Preto (RJ)</t>
-  </si>
-  <si>
-    <t>São Pedro da Aldeia (RJ)</t>
-  </si>
-  <si>
-    <t>São Sebastião do Alto (RJ)</t>
-  </si>
-  <si>
-    <t>Sapucaia (RJ)</t>
-  </si>
-  <si>
-    <t>Saquarema (RJ)</t>
-  </si>
-  <si>
-    <t>Seropédica (RJ)</t>
-  </si>
-  <si>
-    <t>Silva Jardim (RJ)</t>
-  </si>
-  <si>
-    <t>Sumidouro (RJ)</t>
-  </si>
-  <si>
-    <t>Tanguá (RJ)</t>
-  </si>
-  <si>
-    <t>Teresópolis (RJ)</t>
-  </si>
-  <si>
-    <t>Trajano de Moraes (RJ)</t>
-  </si>
-  <si>
-    <t>Três Rios (RJ)</t>
-  </si>
-  <si>
-    <t>Valença (RJ)</t>
-  </si>
-  <si>
-    <t>Varre-Sai (RJ)</t>
-  </si>
-  <si>
-    <t>Vassouras (RJ)</t>
-  </si>
-  <si>
-    <t>Volta Redonda (RJ)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -639,207 +394,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bom" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Célula Vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Ênfase1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Ênfase2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Ênfase3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Ênfase4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -852,9 +419,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -862,44 +429,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -927,31 +494,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -979,26 +529,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1007,211 +540,240 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B68F080A-EC6A-46EF-8B63-526ACC82EDCC}">
-  <dimension ref="A1:O93"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1">
-        <v>2010</v>
-      </c>
-      <c r="E1">
-        <v>2011</v>
-      </c>
-      <c r="F1">
-        <v>2012</v>
-      </c>
-      <c r="G1">
-        <v>2013</v>
-      </c>
-      <c r="H1">
-        <v>2014</v>
-      </c>
-      <c r="I1">
-        <v>2015</v>
-      </c>
-      <c r="J1">
-        <v>2016</v>
-      </c>
-      <c r="K1">
-        <v>2017</v>
-      </c>
-      <c r="L1">
-        <v>2018</v>
-      </c>
-      <c r="M1">
-        <v>2019</v>
-      </c>
-      <c r="N1">
-        <v>2020</v>
-      </c>
-      <c r="O1">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B2">
         <v>3300100</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>6331318</v>
@@ -1249,16 +811,22 @@
       <c r="O2">
         <v>11194157</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2">
+        <v>11032725</v>
+      </c>
+      <c r="Q2">
+        <v>11900498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B3">
         <v>3300159</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>93788</v>
@@ -1296,16 +864,22 @@
       <c r="O3">
         <v>249119</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3">
+        <v>276295</v>
+      </c>
+      <c r="Q3">
+        <v>301129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B4">
         <v>3300209</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>1381762</v>
@@ -1343,16 +917,22 @@
       <c r="O4">
         <v>4234217</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4">
+        <v>9387990</v>
+      </c>
+      <c r="Q4">
+        <v>13156181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B5">
         <v>3300225</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>291121</v>
@@ -1390,16 +970,22 @@
       <c r="O5">
         <v>427436</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5">
+        <v>488446</v>
+      </c>
+      <c r="Q5">
+        <v>597072</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B6">
         <v>3300233</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>1869297</v>
@@ -1437,16 +1023,22 @@
       <c r="O6">
         <v>2970297</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6">
+        <v>4138737</v>
+      </c>
+      <c r="Q6">
+        <v>5019621</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B7">
         <v>3300258</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>400094</v>
@@ -1484,16 +1076,22 @@
       <c r="O7">
         <v>2705450</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7">
+        <v>7026277</v>
+      </c>
+      <c r="Q7">
+        <v>9335374</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B8">
         <v>3300308</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>1473284</v>
@@ -1531,16 +1129,22 @@
       <c r="O8">
         <v>2713890</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8">
+        <v>3005432</v>
+      </c>
+      <c r="Q8">
+        <v>3225723</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B9">
         <v>3300407</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>3460173</v>
@@ -1578,16 +1182,22 @@
       <c r="O9">
         <v>6449270</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9">
+        <v>6513674</v>
+      </c>
+      <c r="Q9">
+        <v>6831115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B10">
         <v>3300456</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>4427124</v>
@@ -1625,16 +1235,22 @@
       <c r="O10">
         <v>8839736</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10">
+        <v>9579716</v>
+      </c>
+      <c r="Q10">
+        <v>9686339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B11">
         <v>3300506</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>404187</v>
@@ -1672,16 +1288,22 @@
       <c r="O11">
         <v>887295</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11">
+        <v>890883</v>
+      </c>
+      <c r="Q11">
+        <v>1018920</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B12">
         <v>3300605</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>420564</v>
@@ -1719,16 +1341,22 @@
       <c r="O12">
         <v>908156</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12">
+        <v>1062573</v>
+      </c>
+      <c r="Q12">
+        <v>1207611</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B13">
         <v>3300704</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>9301079</v>
@@ -1766,16 +1394,22 @@
       <c r="O13">
         <v>12359509</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13">
+        <v>15453319</v>
+      </c>
+      <c r="Q13">
+        <v>16964472</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B14">
         <v>3300803</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>906006</v>
@@ -1813,16 +1447,22 @@
       <c r="O14">
         <v>1305498</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14">
+        <v>1567755</v>
+      </c>
+      <c r="Q14">
+        <v>1702402</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B15">
         <v>3300902</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>167262</v>
@@ -1860,16 +1500,22 @@
       <c r="O15">
         <v>399847</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15">
+        <v>459442</v>
+      </c>
+      <c r="Q15">
+        <v>479568</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B16">
         <v>3300936</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D16">
         <v>604027</v>
@@ -1907,16 +1553,22 @@
       <c r="O16">
         <v>726756</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16">
+        <v>1195363</v>
+      </c>
+      <c r="Q16">
+        <v>1045633</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B17">
         <v>3300951</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D17">
         <v>208944</v>
@@ -1954,16 +1606,22 @@
       <c r="O17">
         <v>603969</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17">
+        <v>572680</v>
+      </c>
+      <c r="Q17">
+        <v>633562</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B18">
         <v>3301009</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D18">
         <v>38684389</v>
@@ -2001,16 +1659,22 @@
       <c r="O18">
         <v>37179716</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18">
+        <v>49942074</v>
+      </c>
+      <c r="Q18">
+        <v>42953469</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B19">
         <v>3301108</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D19">
         <v>722818</v>
@@ -2048,16 +1712,22 @@
       <c r="O19">
         <v>841413</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19">
+        <v>915904</v>
+      </c>
+      <c r="Q19">
+        <v>1075296</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B20">
         <v>3301157</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>116154</v>
@@ -2095,16 +1765,22 @@
       <c r="O20">
         <v>395476</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20">
+        <v>383126</v>
+      </c>
+      <c r="Q20">
+        <v>393125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B21">
         <v>3301207</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D21">
         <v>266203</v>
@@ -2142,16 +1818,22 @@
       <c r="O21">
         <v>561273</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21">
+        <v>620952</v>
+      </c>
+      <c r="Q21">
+        <v>671866</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B22">
         <v>3301306</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D22">
         <v>2071660</v>
@@ -2189,16 +1871,22 @@
       <c r="O22">
         <v>2352145</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22">
+        <v>3142865</v>
+      </c>
+      <c r="Q22">
+        <v>3363239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B23">
         <v>3301405</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D23">
         <v>179532</v>
@@ -2236,16 +1924,22 @@
       <c r="O23">
         <v>434135</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23">
+        <v>449935</v>
+      </c>
+      <c r="Q23">
+        <v>504000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B24">
         <v>3301504</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D24">
         <v>211282</v>
@@ -2283,16 +1977,22 @@
       <c r="O24">
         <v>456168</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24">
+        <v>477136</v>
+      </c>
+      <c r="Q24">
+        <v>530533</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B25">
         <v>3301603</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D25">
         <v>106324</v>
@@ -2330,16 +2030,22 @@
       <c r="O25">
         <v>249214</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25">
+        <v>274030</v>
+      </c>
+      <c r="Q25">
+        <v>285448</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B26">
         <v>3301702</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D26">
         <v>23107679</v>
@@ -2377,16 +2083,22 @@
       <c r="O26">
         <v>53136504</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26">
+        <v>65861333</v>
+      </c>
+      <c r="Q26">
+        <v>70068007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B27">
         <v>3301801</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D27">
         <v>168677</v>
@@ -2424,16 +2136,22 @@
       <c r="O27">
         <v>406735</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27">
+        <v>383264</v>
+      </c>
+      <c r="Q27">
+        <v>320438</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B28">
         <v>3301850</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D28">
         <v>620368</v>
@@ -2471,16 +2189,22 @@
       <c r="O28">
         <v>1363992</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28">
+        <v>1450030</v>
+      </c>
+      <c r="Q28">
+        <v>1589983</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B29">
         <v>3301876</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D29">
         <v>213966</v>
@@ -2518,16 +2242,22 @@
       <c r="O29">
         <v>631393</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29">
+        <v>712149</v>
+      </c>
+      <c r="Q29">
+        <v>814661</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B30">
         <v>3301900</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D30">
         <v>2429729</v>
@@ -2565,16 +2295,22 @@
       <c r="O30">
         <v>5640678</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30">
+        <v>5640941</v>
+      </c>
+      <c r="Q30">
+        <v>6278393</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B31">
         <v>3302007</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D31">
         <v>4649831</v>
@@ -2612,16 +2348,22 @@
       <c r="O31">
         <v>10502682</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31">
+        <v>9092302</v>
+      </c>
+      <c r="Q31">
+        <v>11383962</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B32">
         <v>3302056</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D32">
         <v>163482</v>
@@ -2659,16 +2401,22 @@
       <c r="O32">
         <v>418759</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32">
+        <v>399061</v>
+      </c>
+      <c r="Q32">
+        <v>431493</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B33">
         <v>3302106</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D33">
         <v>256885</v>
@@ -2706,16 +2454,22 @@
       <c r="O33">
         <v>635888</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33">
+        <v>685897</v>
+      </c>
+      <c r="Q33">
+        <v>756489</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B34">
         <v>3302205</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D34">
         <v>1436222</v>
@@ -2753,16 +2507,22 @@
       <c r="O34">
         <v>3394940</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P34">
+        <v>3597510</v>
+      </c>
+      <c r="Q34">
+        <v>4067637</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B35">
         <v>3302254</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D35">
         <v>1495063</v>
@@ -2800,16 +2560,22 @@
       <c r="O35">
         <v>6893408</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35">
+        <v>6268879</v>
+      </c>
+      <c r="Q35">
+        <v>6988685</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B36">
         <v>3302270</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D36">
         <v>692967</v>
@@ -2847,16 +2613,22 @@
       <c r="O36">
         <v>1530183</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P36">
+        <v>1669777</v>
+      </c>
+      <c r="Q36">
+        <v>1874798</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B37">
         <v>3302304</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D37">
         <v>77640</v>
@@ -2894,16 +2666,22 @@
       <c r="O37">
         <v>184160</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P37">
+        <v>191370</v>
+      </c>
+      <c r="Q37">
+        <v>208603</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B38">
         <v>3302403</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D38">
         <v>13613373</v>
@@ -2941,16 +2719,22 @@
       <c r="O38">
         <v>17746787</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P38">
+        <v>19614198</v>
+      </c>
+      <c r="Q38">
+        <v>22394860</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B39">
         <v>3302452</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D39">
         <v>94084</v>
@@ -2988,16 +2772,22 @@
       <c r="O39">
         <v>214870</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P39">
+        <v>277379</v>
+      </c>
+      <c r="Q39">
+        <v>282626</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B40">
         <v>3302502</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>2372395</v>
@@ -3035,16 +2825,22 @@
       <c r="O40">
         <v>4765781</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P40">
+        <v>4780409</v>
+      </c>
+      <c r="Q40">
+        <v>5301411</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B41">
         <v>3302601</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D41">
         <v>1772367</v>
@@ -3082,16 +2878,22 @@
       <c r="O41">
         <v>3211861</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P41">
+        <v>3079416</v>
+      </c>
+      <c r="Q41">
+        <v>3443660</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B42">
         <v>3302700</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D42">
         <v>1873273</v>
@@ -3129,16 +2931,22 @@
       <c r="O42">
         <v>85814188</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P42">
+        <v>158394291</v>
+      </c>
+      <c r="Q42">
+        <v>134092034</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B43">
         <v>3302809</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D43">
         <v>172472</v>
@@ -3176,16 +2984,22 @@
       <c r="O43">
         <v>357688</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P43">
+        <v>438826</v>
+      </c>
+      <c r="Q43">
+        <v>444764</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B44">
         <v>3302858</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D44">
         <v>1452834</v>
@@ -3223,16 +3037,22 @@
       <c r="O44">
         <v>2619212</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P44">
+        <v>2834791</v>
+      </c>
+      <c r="Q44">
+        <v>3029007</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B45">
         <v>3302908</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D45">
         <v>359764</v>
@@ -3270,16 +3090,22 @@
       <c r="O45">
         <v>632498</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P45">
+        <v>760561</v>
+      </c>
+      <c r="Q45">
+        <v>847198</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B46">
         <v>3303005</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D46">
         <v>248305</v>
@@ -3317,16 +3143,22 @@
       <c r="O46">
         <v>662180</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P46">
+        <v>725936</v>
+      </c>
+      <c r="Q46">
+        <v>742077</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B47">
         <v>3303104</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D47">
         <v>152230</v>
@@ -3364,16 +3196,22 @@
       <c r="O47">
         <v>324261</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P47">
+        <v>377914</v>
+      </c>
+      <c r="Q47">
+        <v>408436</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B48">
         <v>3303203</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D48">
         <v>1709866</v>
@@ -3411,16 +3249,22 @@
       <c r="O48">
         <v>3059459</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P48">
+        <v>3389447</v>
+      </c>
+      <c r="Q48">
+        <v>3339769</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B49">
         <v>3303302</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D49">
         <v>12587901</v>
@@ -3458,16 +3302,22 @@
       <c r="O49">
         <v>66345488</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P49">
+        <v>88716289</v>
+      </c>
+      <c r="Q49">
+        <v>76268005</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B50">
         <v>3303401</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D50">
         <v>2921047</v>
@@ -3505,16 +3355,22 @@
       <c r="O50">
         <v>6324877</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P50">
+        <v>6774950</v>
+      </c>
+      <c r="Q50">
+        <v>7367567</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B51">
         <v>3303500</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D51">
         <v>10142818</v>
@@ -3552,16 +3408,22 @@
       <c r="O51">
         <v>17794452</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P51">
+        <v>19911894</v>
+      </c>
+      <c r="Q51">
+        <v>20518624</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B52">
         <v>3303609</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D52">
         <v>450653</v>
@@ -3599,16 +3461,22 @@
       <c r="O52">
         <v>1162875</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P52">
+        <v>1073592</v>
+      </c>
+      <c r="Q52">
+        <v>1085489</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B53">
         <v>3303708</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D53">
         <v>572304</v>
@@ -3646,16 +3514,22 @@
       <c r="O53">
         <v>1253017</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P53">
+        <v>1254488</v>
+      </c>
+      <c r="Q53">
+        <v>1399157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B54">
         <v>3303807</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D54">
         <v>809203</v>
@@ -3693,16 +3567,22 @@
       <c r="O54">
         <v>1955280</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P54">
+        <v>4426137</v>
+      </c>
+      <c r="Q54">
+        <v>6324392</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B55">
         <v>3303856</v>
       </c>
       <c r="C55" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D55">
         <v>285723</v>
@@ -3740,16 +3620,22 @@
       <c r="O55">
         <v>684851</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P55">
+        <v>793141</v>
+      </c>
+      <c r="Q55">
+        <v>862740</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B56">
         <v>3303906</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D56">
         <v>7244425</v>
@@ -3787,16 +3673,22 @@
       <c r="O56">
         <v>15665370</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P56">
+        <v>15951213</v>
+      </c>
+      <c r="Q56">
+        <v>19907335</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B57">
         <v>3303955</v>
       </c>
       <c r="C57" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D57">
         <v>205712</v>
@@ -3834,16 +3726,22 @@
       <c r="O57">
         <v>1452638</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P57">
+        <v>1207568</v>
+      </c>
+      <c r="Q57">
+        <v>1187697</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B58">
         <v>3304003</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D58">
         <v>1045134</v>
@@ -3881,16 +3779,22 @@
       <c r="O58">
         <v>2449973</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P58">
+        <v>2885734</v>
+      </c>
+      <c r="Q58">
+        <v>3388747</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B59">
         <v>3304102</v>
       </c>
       <c r="C59" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D59">
         <v>180948</v>
@@ -3928,16 +3832,22 @@
       <c r="O59">
         <v>415943</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P59">
+        <v>564478</v>
+      </c>
+      <c r="Q59">
+        <v>559253</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B60">
         <v>3304110</v>
       </c>
       <c r="C60" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D60">
         <v>5174746</v>
@@ -3975,16 +3885,22 @@
       <c r="O60">
         <v>4245725</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P60">
+        <v>3956993</v>
+      </c>
+      <c r="Q60">
+        <v>3205582</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B61">
         <v>3304128</v>
       </c>
       <c r="C61" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D61">
         <v>270826</v>
@@ -4022,16 +3938,22 @@
       <c r="O61">
         <v>305010</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P61">
+        <v>359212</v>
+      </c>
+      <c r="Q61">
+        <v>400781</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B62">
         <v>3304144</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D62">
         <v>2032471</v>
@@ -4069,16 +3991,22 @@
       <c r="O62">
         <v>4361684</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P62">
+        <v>4403902</v>
+      </c>
+      <c r="Q62">
+        <v>4938812</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B63">
         <v>3304151</v>
       </c>
       <c r="C63" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D63">
         <v>3791122</v>
@@ -4116,16 +4044,22 @@
       <c r="O63">
         <v>5996886</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P63">
+        <v>8493476</v>
+      </c>
+      <c r="Q63">
+        <v>5669644</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B64">
         <v>3304201</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D64">
         <v>5777847</v>
@@ -4163,16 +4097,22 @@
       <c r="O64">
         <v>10754357</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P64">
+        <v>11663534</v>
+      </c>
+      <c r="Q64">
+        <v>12267696</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B65">
         <v>3304300</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D65">
         <v>1168377</v>
@@ -4210,16 +4150,22 @@
       <c r="O65">
         <v>1831391</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P65">
+        <v>1905833</v>
+      </c>
+      <c r="Q65">
+        <v>2038466</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B66">
         <v>3304409</v>
       </c>
       <c r="C66" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D66">
         <v>206378</v>
@@ -4257,16 +4203,22 @@
       <c r="O66">
         <v>435959</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P66">
+        <v>558687</v>
+      </c>
+      <c r="Q66">
+        <v>577431</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B67">
         <v>3304508</v>
       </c>
       <c r="C67" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D67">
         <v>291757</v>
@@ -4304,16 +4256,22 @@
       <c r="O67">
         <v>294384</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P67">
+        <v>325931</v>
+      </c>
+      <c r="Q67">
+        <v>338695</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B68">
         <v>3304524</v>
       </c>
       <c r="C68" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D68">
         <v>8957877</v>
@@ -4351,16 +4309,22 @@
       <c r="O68">
         <v>8948996</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P68">
+        <v>10916617</v>
+      </c>
+      <c r="Q68">
+        <v>10599898</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B69">
         <v>3304557</v>
       </c>
       <c r="C69" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D69">
         <v>208153595</v>
@@ -4398,16 +4362,22 @@
       <c r="O69">
         <v>359632648</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P69">
+        <v>380381515</v>
+      </c>
+      <c r="Q69">
+        <v>418462360</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B70">
         <v>3304607</v>
       </c>
       <c r="C70" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D70">
         <v>136012</v>
@@ -4445,16 +4415,22 @@
       <c r="O70">
         <v>234575</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P70">
+        <v>267049</v>
+      </c>
+      <c r="Q70">
+        <v>275098</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B71">
         <v>3304706</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D71">
         <v>584056</v>
@@ -4492,16 +4468,22 @@
       <c r="O71">
         <v>1284632</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P71">
+        <v>1457559</v>
+      </c>
+      <c r="Q71">
+        <v>1686337</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B72">
         <v>3304755</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D72">
         <v>476294</v>
@@ -4539,16 +4521,22 @@
       <c r="O72">
         <v>1184513</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P72">
+        <v>1305146</v>
+      </c>
+      <c r="Q72">
+        <v>1481367</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B73">
         <v>3304805</v>
       </c>
       <c r="C73" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D73">
         <v>392106</v>
@@ -4586,16 +4574,22 @@
       <c r="O73">
         <v>845178</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P73">
+        <v>921818</v>
+      </c>
+      <c r="Q73">
+        <v>985938</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B74">
         <v>3304904</v>
       </c>
       <c r="C74" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D74">
         <v>10327201</v>
@@ -4633,16 +4627,22 @@
       <c r="O74">
         <v>20324752</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P74">
+        <v>20561718</v>
+      </c>
+      <c r="Q74">
+        <v>23063689</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B75">
         <v>3305000</v>
       </c>
       <c r="C75" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D75">
         <v>6099729</v>
@@ -4680,16 +4680,22 @@
       <c r="O75">
         <v>9886849</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P75">
+        <v>12793325</v>
+      </c>
+      <c r="Q75">
+        <v>13986152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B76">
         <v>3305109</v>
       </c>
       <c r="C76" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D76">
         <v>5015432</v>
@@ -4727,16 +4733,22 @@
       <c r="O76">
         <v>8963716</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P76">
+        <v>10615039</v>
+      </c>
+      <c r="Q76">
+        <v>11534047</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B77">
         <v>3305133</v>
       </c>
       <c r="C77" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D77">
         <v>70522</v>
@@ -4774,16 +4786,22 @@
       <c r="O77">
         <v>196857</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P77">
+        <v>238089</v>
+      </c>
+      <c r="Q77">
+        <v>232730</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B78">
         <v>3305158</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D78">
         <v>597026</v>
@@ -4821,16 +4839,22 @@
       <c r="O78">
         <v>744334</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P78">
+        <v>914557</v>
+      </c>
+      <c r="Q78">
+        <v>941645</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B79">
         <v>3305208</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D79">
         <v>929226</v>
@@ -4868,16 +4892,22 @@
       <c r="O79">
         <v>2743637</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P79">
+        <v>2975703</v>
+      </c>
+      <c r="Q79">
+        <v>3359011</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B80">
         <v>3305307</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D80">
         <v>134864</v>
@@ -4915,16 +4945,22 @@
       <c r="O80">
         <v>241281</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P80">
+        <v>275485</v>
+      </c>
+      <c r="Q80">
+        <v>272845</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B81">
         <v>3305406</v>
       </c>
       <c r="C81" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D81">
         <v>440636</v>
@@ -4962,16 +4998,22 @@
       <c r="O81">
         <v>1000567</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P81">
+        <v>1115045</v>
+      </c>
+      <c r="Q81">
+        <v>1227721</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B82">
         <v>3305505</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D82">
         <v>1464446</v>
@@ -5009,16 +5051,22 @@
       <c r="O82">
         <v>42178159</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P82">
+        <v>75409090</v>
+      </c>
+      <c r="Q82">
+        <v>64701140</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B83">
         <v>3305554</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D83">
         <v>840825</v>
@@ -5056,16 +5104,22 @@
       <c r="O83">
         <v>4777005</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P83">
+        <v>4240104</v>
+      </c>
+      <c r="Q83">
+        <v>3760076</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B84">
         <v>3305604</v>
       </c>
       <c r="C84" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D84">
         <v>225491</v>
@@ -5103,16 +5157,22 @@
       <c r="O84">
         <v>602627</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P84">
+        <v>646129</v>
+      </c>
+      <c r="Q84">
+        <v>705912</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B85">
         <v>3305703</v>
       </c>
       <c r="C85" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D85">
         <v>206676</v>
@@ -5150,16 +5210,22 @@
       <c r="O85">
         <v>600250</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P85">
+        <v>675215</v>
+      </c>
+      <c r="Q85">
+        <v>733841</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B86">
         <v>3305752</v>
       </c>
       <c r="C86" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D86">
         <v>340479</v>
@@ -5197,16 +5263,22 @@
       <c r="O86">
         <v>694534</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P86">
+        <v>807845</v>
+      </c>
+      <c r="Q86">
+        <v>858815</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B87">
         <v>3305802</v>
       </c>
       <c r="C87" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D87">
         <v>2896778</v>
@@ -5244,16 +5316,22 @@
       <c r="O87">
         <v>5923899</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P87">
+        <v>6247785</v>
+      </c>
+      <c r="Q87">
+        <v>7104546</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B88">
         <v>3305901</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D88">
         <v>89335</v>
@@ -5291,16 +5369,22 @@
       <c r="O88">
         <v>242013</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P88">
+        <v>277260</v>
+      </c>
+      <c r="Q88">
+        <v>290439</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B89">
         <v>3306008</v>
       </c>
       <c r="C89" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D89">
         <v>1835764</v>
@@ -5338,16 +5422,22 @@
       <c r="O89">
         <v>6348140</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P89">
+        <v>5499387</v>
+      </c>
+      <c r="Q89">
+        <v>6017636</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B90">
         <v>3306107</v>
       </c>
       <c r="C90" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D90">
         <v>1022596</v>
@@ -5385,16 +5475,22 @@
       <c r="O90">
         <v>3122592</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P90">
+        <v>3044054</v>
+      </c>
+      <c r="Q90">
+        <v>3104489</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B91">
         <v>3306156</v>
       </c>
       <c r="C91" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D91">
         <v>82212</v>
@@ -5432,16 +5528,22 @@
       <c r="O91">
         <v>264149</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P91">
+        <v>399232</v>
+      </c>
+      <c r="Q91">
+        <v>407915</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B92">
         <v>3306206</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D92">
         <v>491051</v>
@@ -5479,16 +5581,22 @@
       <c r="O92">
         <v>1321254</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P92">
+        <v>1344715</v>
+      </c>
+      <c r="Q92">
+        <v>1472880</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="B93">
         <v>3306305</v>
       </c>
       <c r="C93" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D93">
         <v>9656616</v>
@@ -5526,8 +5634,14 @@
       <c r="O93">
         <v>19671203</v>
       </c>
+      <c r="P93">
+        <v>15472607</v>
+      </c>
+      <c r="Q93">
+        <v>15307615</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>